--- a/public/test-data/03_2026_하반기_피어리뷰_정하늘.xlsx
+++ b/public/test-data/03_2026_하반기_피어리뷰_정하늘.xlsx
@@ -2,11 +2,11 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="안내" sheetId="1" r:id="R9f54b8266a5048ec"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="_메타" sheetId="2" r:id="R49680bba4a094cf7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="1_신규 랜딩페이지 제작" sheetId="3" r:id="R3d73371e8e004f50"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2_Cloud X 메인 UX 개선" sheetId="4" r:id="R547feecc24864db4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3_내부 협업툴 정비" sheetId="5" r:id="R2c797c52d3534b30"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="안내" sheetId="1" r:id="R649ffeb41a694247"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="_메타" sheetId="2" r:id="R8137b4bb83e64c05"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="1_신규 랜딩페이지 제작" sheetId="3" r:id="R8addca2f51d74a34"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2_Cloud X 메인 UX 개선" sheetId="4" r:id="R5d30ffbb33434bda"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3_내부 협업툴 정비" sheetId="5" r:id="R44b48719e6ad4f07"/>
   </x:sheets>
 </x:workbook>
 </file>
